--- a/artfynd/A 28351-2025 artfynd.xlsx
+++ b/artfynd/A 28351-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127110765</v>
+        <v>127110833</v>
       </c>
       <c r="B2" t="n">
-        <v>79632</v>
+        <v>92615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620370</v>
+        <v>620366</v>
       </c>
       <c r="R2" t="n">
-        <v>7324248</v>
+        <v>7324246</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127110833</v>
+        <v>127111152</v>
       </c>
       <c r="B3" t="n">
-        <v>92615</v>
+        <v>79603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620366</v>
+        <v>620361</v>
       </c>
       <c r="R3" t="n">
-        <v>7324246</v>
+        <v>7324257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127111152</v>
+        <v>127110765</v>
       </c>
       <c r="B4" t="n">
-        <v>79603</v>
+        <v>79632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620361</v>
+        <v>620370</v>
       </c>
       <c r="R4" t="n">
-        <v>7324257</v>
+        <v>7324248</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127111125</v>
+        <v>127111072</v>
       </c>
       <c r="B14" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620361</v>
+        <v>620376</v>
       </c>
       <c r="R14" t="n">
-        <v>7324257</v>
+        <v>7324244</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127111072</v>
+        <v>127111125</v>
       </c>
       <c r="B15" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620376</v>
+        <v>620361</v>
       </c>
       <c r="R15" t="n">
-        <v>7324244</v>
+        <v>7324257</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 28351-2025 artfynd.xlsx
+++ b/artfynd/A 28351-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127111152</v>
+        <v>127110765</v>
       </c>
       <c r="B3" t="n">
-        <v>79603</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620361</v>
+        <v>620370</v>
       </c>
       <c r="R3" t="n">
-        <v>7324257</v>
+        <v>7324248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127110765</v>
+        <v>127111152</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>79603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620370</v>
+        <v>620361</v>
       </c>
       <c r="R4" t="n">
-        <v>7324248</v>
+        <v>7324257</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 28351-2025 artfynd.xlsx
+++ b/artfynd/A 28351-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127110833</v>
+        <v>127110765</v>
       </c>
       <c r="B2" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620366</v>
+        <v>620370</v>
       </c>
       <c r="R2" t="n">
-        <v>7324246</v>
+        <v>7324248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127110765</v>
+        <v>127110833</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620370</v>
+        <v>620366</v>
       </c>
       <c r="R3" t="n">
-        <v>7324248</v>
+        <v>7324246</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>127111854</v>
       </c>
       <c r="B7" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127111897</v>
       </c>
       <c r="B10" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127111544</v>
       </c>
       <c r="B11" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127111954</v>
       </c>
       <c r="B12" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127111072</v>
+        <v>127111125</v>
       </c>
       <c r="B14" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620376</v>
+        <v>620361</v>
       </c>
       <c r="R14" t="n">
-        <v>7324244</v>
+        <v>7324257</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127111125</v>
+        <v>127111072</v>
       </c>
       <c r="B15" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620361</v>
+        <v>620376</v>
       </c>
       <c r="R15" t="n">
-        <v>7324257</v>
+        <v>7324244</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 28351-2025 artfynd.xlsx
+++ b/artfynd/A 28351-2025 artfynd.xlsx
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127111125</v>
+        <v>127111072</v>
       </c>
       <c r="B14" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620361</v>
+        <v>620376</v>
       </c>
       <c r="R14" t="n">
-        <v>7324257</v>
+        <v>7324244</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127111072</v>
+        <v>127111125</v>
       </c>
       <c r="B15" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620376</v>
+        <v>620361</v>
       </c>
       <c r="R15" t="n">
-        <v>7324244</v>
+        <v>7324257</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 28351-2025 artfynd.xlsx
+++ b/artfynd/A 28351-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110765</v>
       </c>
       <c r="B2" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127110833</v>
+        <v>127111152</v>
       </c>
       <c r="B3" t="n">
-        <v>92616</v>
+        <v>79607</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620366</v>
+        <v>620361</v>
       </c>
       <c r="R3" t="n">
-        <v>7324246</v>
+        <v>7324257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127111152</v>
+        <v>127110833</v>
       </c>
       <c r="B4" t="n">
-        <v>79603</v>
+        <v>92620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620361</v>
+        <v>620366</v>
       </c>
       <c r="R4" t="n">
-        <v>7324257</v>
+        <v>7324246</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>127111639</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127111264</v>
       </c>
       <c r="B6" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127111854</v>
       </c>
       <c r="B7" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>127110627</v>
       </c>
       <c r="B8" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>127111445</v>
       </c>
       <c r="B9" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127111897</v>
       </c>
       <c r="B10" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127111544</v>
       </c>
       <c r="B11" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127111954</v>
       </c>
       <c r="B12" t="n">
-        <v>91587</v>
+        <v>91591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>127111418</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127111072</v>
+        <v>127111125</v>
       </c>
       <c r="B14" t="n">
-        <v>79632</v>
+        <v>78685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620376</v>
+        <v>620361</v>
       </c>
       <c r="R14" t="n">
-        <v>7324244</v>
+        <v>7324257</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127111125</v>
+        <v>127111072</v>
       </c>
       <c r="B15" t="n">
-        <v>78681</v>
+        <v>79636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620361</v>
+        <v>620376</v>
       </c>
       <c r="R15" t="n">
-        <v>7324257</v>
+        <v>7324244</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 28351-2025 artfynd.xlsx
+++ b/artfynd/A 28351-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127111152</v>
+        <v>127110833</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>92620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620361</v>
+        <v>620366</v>
       </c>
       <c r="R3" t="n">
-        <v>7324257</v>
+        <v>7324246</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127110833</v>
+        <v>127111152</v>
       </c>
       <c r="B4" t="n">
-        <v>92620</v>
+        <v>79607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620366</v>
+        <v>620361</v>
       </c>
       <c r="R4" t="n">
-        <v>7324246</v>
+        <v>7324257</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 28351-2025 artfynd.xlsx
+++ b/artfynd/A 28351-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127110765</v>
+        <v>127110833</v>
       </c>
       <c r="B2" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620370</v>
+        <v>620366</v>
       </c>
       <c r="R2" t="n">
-        <v>7324248</v>
+        <v>7324246</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127110833</v>
+        <v>127110765</v>
       </c>
       <c r="B3" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620366</v>
+        <v>620370</v>
       </c>
       <c r="R3" t="n">
-        <v>7324246</v>
+        <v>7324248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 28351-2025 artfynd.xlsx
+++ b/artfynd/A 28351-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110833</v>
       </c>
       <c r="B2" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127110765</v>
+        <v>127111152</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>79609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620370</v>
+        <v>620361</v>
       </c>
       <c r="R3" t="n">
-        <v>7324248</v>
+        <v>7324257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127111152</v>
+        <v>127110765</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>79638</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620361</v>
+        <v>620370</v>
       </c>
       <c r="R4" t="n">
-        <v>7324257</v>
+        <v>7324248</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>127111639</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127111264</v>
       </c>
       <c r="B6" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127111854</v>
       </c>
       <c r="B7" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>127110627</v>
       </c>
       <c r="B8" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>127111445</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127111897</v>
       </c>
       <c r="B10" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127111544</v>
       </c>
       <c r="B11" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127111954</v>
       </c>
       <c r="B12" t="n">
-        <v>91591</v>
+        <v>91593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>127111418</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>127111125</v>
       </c>
       <c r="B14" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>127111072</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28351-2025 artfynd.xlsx
+++ b/artfynd/A 28351-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127110833</v>
+        <v>127111152</v>
       </c>
       <c r="B2" t="n">
-        <v>92622</v>
+        <v>79609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620366</v>
+        <v>620361</v>
       </c>
       <c r="R2" t="n">
-        <v>7324246</v>
+        <v>7324257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127111152</v>
+        <v>127110833</v>
       </c>
       <c r="B3" t="n">
-        <v>79609</v>
+        <v>92622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620361</v>
+        <v>620366</v>
       </c>
       <c r="R3" t="n">
-        <v>7324257</v>
+        <v>7324246</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 28351-2025 artfynd.xlsx
+++ b/artfynd/A 28351-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127111152</v>
+        <v>127110833</v>
       </c>
       <c r="B2" t="n">
-        <v>79609</v>
+        <v>92628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620361</v>
+        <v>620366</v>
       </c>
       <c r="R2" t="n">
-        <v>7324257</v>
+        <v>7324246</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127110833</v>
+        <v>127111152</v>
       </c>
       <c r="B3" t="n">
-        <v>92622</v>
+        <v>79609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620366</v>
+        <v>620361</v>
       </c>
       <c r="R3" t="n">
-        <v>7324246</v>
+        <v>7324257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>127111854</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127111897</v>
       </c>
       <c r="B10" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127111544</v>
       </c>
       <c r="B11" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127111954</v>
       </c>
       <c r="B12" t="n">
-        <v>91593</v>
+        <v>91599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127111125</v>
+        <v>127111072</v>
       </c>
       <c r="B14" t="n">
-        <v>78687</v>
+        <v>79638</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620361</v>
+        <v>620376</v>
       </c>
       <c r="R14" t="n">
-        <v>7324257</v>
+        <v>7324244</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127111072</v>
+        <v>127111125</v>
       </c>
       <c r="B15" t="n">
-        <v>79638</v>
+        <v>78687</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620376</v>
+        <v>620361</v>
       </c>
       <c r="R15" t="n">
-        <v>7324244</v>
+        <v>7324257</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 28351-2025 artfynd.xlsx
+++ b/artfynd/A 28351-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127110833</v>
+        <v>127111152</v>
       </c>
       <c r="B2" t="n">
-        <v>92628</v>
+        <v>79612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620366</v>
+        <v>620361</v>
       </c>
       <c r="R2" t="n">
-        <v>7324246</v>
+        <v>7324257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127111152</v>
+        <v>127110833</v>
       </c>
       <c r="B3" t="n">
-        <v>79609</v>
+        <v>92631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620361</v>
+        <v>620366</v>
       </c>
       <c r="R3" t="n">
-        <v>7324257</v>
+        <v>7324246</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>127110765</v>
       </c>
       <c r="B4" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127111639</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127111264</v>
       </c>
       <c r="B6" t="n">
-        <v>78426</v>
+        <v>78429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127111854</v>
       </c>
       <c r="B7" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>127110627</v>
       </c>
       <c r="B8" t="n">
-        <v>78426</v>
+        <v>78429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>127111445</v>
       </c>
       <c r="B9" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127111897</v>
       </c>
       <c r="B10" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127111544</v>
       </c>
       <c r="B11" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127111954</v>
       </c>
       <c r="B12" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>127111418</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>127111072</v>
       </c>
       <c r="B14" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>127111125</v>
       </c>
       <c r="B15" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28351-2025 artfynd.xlsx
+++ b/artfynd/A 28351-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127111152</v>
       </c>
       <c r="B2" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127110833</v>
       </c>
       <c r="B3" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127110765</v>
       </c>
       <c r="B4" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127111639</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127111264</v>
       </c>
       <c r="B6" t="n">
-        <v>78429</v>
+        <v>78435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127111854</v>
       </c>
       <c r="B7" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>127110627</v>
       </c>
       <c r="B8" t="n">
-        <v>78429</v>
+        <v>78435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>127111445</v>
       </c>
       <c r="B9" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127111897</v>
       </c>
       <c r="B10" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127111544</v>
       </c>
       <c r="B11" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127111954</v>
       </c>
       <c r="B12" t="n">
-        <v>91602</v>
+        <v>91610</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>127111418</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127111072</v>
+        <v>127111125</v>
       </c>
       <c r="B14" t="n">
-        <v>79641</v>
+        <v>78696</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620376</v>
+        <v>620361</v>
       </c>
       <c r="R14" t="n">
-        <v>7324244</v>
+        <v>7324257</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127111125</v>
+        <v>127111072</v>
       </c>
       <c r="B15" t="n">
-        <v>78690</v>
+        <v>79647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620361</v>
+        <v>620376</v>
       </c>
       <c r="R15" t="n">
-        <v>7324257</v>
+        <v>7324244</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 28351-2025 artfynd.xlsx
+++ b/artfynd/A 28351-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127111152</v>
+        <v>127110833</v>
       </c>
       <c r="B2" t="n">
-        <v>79618</v>
+        <v>92609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620361</v>
+        <v>620366</v>
       </c>
       <c r="R2" t="n">
-        <v>7324257</v>
+        <v>7324246</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127110833</v>
+        <v>127110765</v>
       </c>
       <c r="B3" t="n">
-        <v>92639</v>
+        <v>79629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620366</v>
+        <v>620370</v>
       </c>
       <c r="R3" t="n">
-        <v>7324246</v>
+        <v>7324248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127110765</v>
+        <v>127111152</v>
       </c>
       <c r="B4" t="n">
-        <v>79647</v>
+        <v>79600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620370</v>
+        <v>620361</v>
       </c>
       <c r="R4" t="n">
-        <v>7324248</v>
+        <v>7324257</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>127111639</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127111264</v>
       </c>
       <c r="B6" t="n">
-        <v>78435</v>
+        <v>78417</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127111854</v>
       </c>
       <c r="B7" t="n">
-        <v>91367</v>
+        <v>91337</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>127110627</v>
       </c>
       <c r="B8" t="n">
-        <v>78435</v>
+        <v>78417</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>127111445</v>
       </c>
       <c r="B9" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127111897</v>
       </c>
       <c r="B10" t="n">
-        <v>91349</v>
+        <v>91319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127111544</v>
       </c>
       <c r="B11" t="n">
-        <v>91367</v>
+        <v>91337</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127111954</v>
       </c>
       <c r="B12" t="n">
-        <v>91610</v>
+        <v>91580</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>127111418</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>127111125</v>
       </c>
       <c r="B14" t="n">
-        <v>78696</v>
+        <v>78678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>127111072</v>
       </c>
       <c r="B15" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28351-2025 artfynd.xlsx
+++ b/artfynd/A 28351-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127110833</v>
+        <v>127111152</v>
       </c>
       <c r="B2" t="n">
-        <v>92609</v>
+        <v>79618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620366</v>
+        <v>620361</v>
       </c>
       <c r="R2" t="n">
-        <v>7324246</v>
+        <v>7324257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127110765</v>
+        <v>127110833</v>
       </c>
       <c r="B3" t="n">
-        <v>79629</v>
+        <v>92639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620370</v>
+        <v>620366</v>
       </c>
       <c r="R3" t="n">
-        <v>7324248</v>
+        <v>7324246</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127111152</v>
+        <v>127110765</v>
       </c>
       <c r="B4" t="n">
-        <v>79600</v>
+        <v>79647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620361</v>
+        <v>620370</v>
       </c>
       <c r="R4" t="n">
-        <v>7324257</v>
+        <v>7324248</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>127111639</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127111264</v>
       </c>
       <c r="B6" t="n">
-        <v>78417</v>
+        <v>78435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127111854</v>
       </c>
       <c r="B7" t="n">
-        <v>91337</v>
+        <v>91367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>127110627</v>
       </c>
       <c r="B8" t="n">
-        <v>78417</v>
+        <v>78435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>127111445</v>
       </c>
       <c r="B9" t="n">
-        <v>79629</v>
+        <v>79647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127111897</v>
       </c>
       <c r="B10" t="n">
-        <v>91319</v>
+        <v>91349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127111544</v>
       </c>
       <c r="B11" t="n">
-        <v>91337</v>
+        <v>91367</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127111954</v>
       </c>
       <c r="B12" t="n">
-        <v>91580</v>
+        <v>91610</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>127111418</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>127111125</v>
       </c>
       <c r="B14" t="n">
-        <v>78678</v>
+        <v>78696</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>127111072</v>
       </c>
       <c r="B15" t="n">
-        <v>79629</v>
+        <v>79647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28351-2025 artfynd.xlsx
+++ b/artfynd/A 28351-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127111152</v>
+        <v>127111954</v>
       </c>
       <c r="B2" t="n">
-        <v>79618</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620361</v>
+        <v>620672</v>
       </c>
       <c r="R2" t="n">
-        <v>7324257</v>
+        <v>7324225</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127110833</v>
+        <v>127110893</v>
       </c>
       <c r="B3" t="n">
-        <v>92639</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620366</v>
+        <v>620367</v>
       </c>
       <c r="R3" t="n">
-        <v>7324246</v>
+        <v>7324235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127110765</v>
+        <v>127111125</v>
       </c>
       <c r="B4" t="n">
-        <v>79647</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620370</v>
+        <v>620361</v>
       </c>
       <c r="R4" t="n">
-        <v>7324248</v>
+        <v>7324257</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127111639</v>
+        <v>127111897</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620373</v>
+        <v>620601</v>
       </c>
       <c r="R5" t="n">
-        <v>7324467</v>
+        <v>7324187</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,26 +1047,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1083,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127111264</v>
+        <v>127110833</v>
       </c>
       <c r="B6" t="n">
-        <v>78435</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620355</v>
+        <v>620366</v>
       </c>
       <c r="R6" t="n">
-        <v>7324269</v>
+        <v>7324246</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127111854</v>
+        <v>127111418</v>
       </c>
       <c r="B7" t="n">
-        <v>91367</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620579</v>
+        <v>620372</v>
       </c>
       <c r="R7" t="n">
-        <v>7324208</v>
+        <v>7324436</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127110627</v>
+        <v>127111639</v>
       </c>
       <c r="B8" t="n">
-        <v>78435</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620386</v>
+        <v>620373</v>
       </c>
       <c r="R8" t="n">
-        <v>7324234</v>
+        <v>7324467</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,6 +1338,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127111445</v>
+        <v>127110627</v>
       </c>
       <c r="B9" t="n">
-        <v>79647</v>
+        <v>78730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620335</v>
+        <v>620386</v>
       </c>
       <c r="R9" t="n">
-        <v>7324450</v>
+        <v>7324234</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127111897</v>
+        <v>127111264</v>
       </c>
       <c r="B10" t="n">
-        <v>91349</v>
+        <v>78730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620601</v>
+        <v>620355</v>
       </c>
       <c r="R10" t="n">
-        <v>7324187</v>
+        <v>7324269</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127111544</v>
+        <v>127110765</v>
       </c>
       <c r="B11" t="n">
-        <v>91367</v>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620353</v>
+        <v>620370</v>
       </c>
       <c r="R11" t="n">
-        <v>7324494</v>
+        <v>7324248</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,32 +1665,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127111954</v>
+        <v>127111072</v>
       </c>
       <c r="B12" t="n">
-        <v>91610</v>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620672</v>
+        <v>620376</v>
       </c>
       <c r="R12" t="n">
-        <v>7324225</v>
+        <v>7324244</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127111418</v>
+        <v>127111445</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,21 +1773,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620372</v>
+        <v>620335</v>
       </c>
       <c r="R13" t="n">
-        <v>7324436</v>
+        <v>7324450</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127111125</v>
+        <v>127111152</v>
       </c>
       <c r="B14" t="n">
-        <v>78696</v>
+        <v>79917</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1953,103 +1953,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>127111072</v>
-      </c>
-      <c r="B15" t="n">
-        <v>79647</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Stibma, Stibma, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>620376</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7324244</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28351-2025 artfynd.xlsx
+++ b/artfynd/A 28351-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127111954</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127110893</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127111125</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127111897</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127110833</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127111418</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127111639</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127110627</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127111264</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127110765</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127111072</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127111445</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,8 +2018,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127111152</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>